--- a/events/Krakow_2018_WC/Krakow_2018_WC_start.xlsx
+++ b/events/Krakow_2018_WC/Krakow_2018_WC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W715"/>
+  <dimension ref="A1:AC713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -590,7 +620,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -653,7 +683,7 @@
           <t>CHEN Shiyu</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>84913</t>
         </is>
@@ -716,7 +746,7 @@
           <t>YANG Jie</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>43548</t>
         </is>
@@ -779,7 +809,7 @@
           <t>HENRY Margaux</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>51995</t>
         </is>
@@ -842,7 +872,7 @@
           <t>ROLLINS Harriet</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>64680</t>
         </is>
@@ -905,7 +935,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -968,7 +998,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -1031,7 +1061,7 @@
           <t>DONNELLY Sage</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>60119</t>
         </is>
@@ -1094,7 +1124,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -1157,7 +1187,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -1220,7 +1250,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -1283,7 +1313,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -1346,7 +1376,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -1525,7 +1555,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -1588,7 +1618,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -1651,7 +1681,7 @@
           <t>ZHU Haoran</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>43553</t>
         </is>
@@ -1714,7 +1744,7 @@
           <t>POLACZYK Rafal</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>35083</t>
         </is>
@@ -1777,7 +1807,7 @@
           <t>WOS Michal</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>65063</t>
         </is>
@@ -1840,7 +1870,7 @@
           <t>STANOVSKY Samuel</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>84121</t>
         </is>
@@ -1903,7 +1933,7 @@
           <t>QUEMENEUR Malo</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>60403</t>
         </is>
@@ -1966,7 +1996,7 @@
           <t>RODRIGUES Fabio</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
@@ -2029,7 +2059,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -2092,7 +2122,7 @@
           <t>GUBENKO Nikita</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>39130</t>
         </is>
@@ -2155,7 +2185,7 @@
           <t>KORPES Ren</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>39941</t>
         </is>
@@ -2218,7 +2248,7 @@
           <t>SMITH Tyler</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>51904</t>
         </is>
@@ -2281,7 +2311,7 @@
           <t>KARLSSON Max</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>35111</t>
         </is>
@@ -2344,7 +2374,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -2407,7 +2437,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -2470,7 +2500,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -2533,7 +2563,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -2596,7 +2626,7 @@
           <t>STANOVSKY Jakub</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>41781</t>
         </is>
@@ -2659,7 +2689,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -2722,7 +2752,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -3424,7 +3454,7 @@
           <t>TENG Zhiqiang</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>37089</t>
         </is>
@@ -3482,7 +3512,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -3540,7 +3570,7 @@
           <t>SHKLIARUK Nikolai</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>44025</t>
         </is>
@@ -3598,7 +3628,7 @@
           <t>DA SILVA Kaua</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>60500</t>
         </is>
@@ -3656,7 +3686,7 @@
           <t>ZHANG Genyuan</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>51818</t>
         </is>
@@ -3714,7 +3744,7 @@
           <t>SELBACH JUNIOR Gustavo</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>60496</t>
         </is>
@@ -3772,7 +3802,7 @@
           <t>KHRAMTSOV Dmitrii</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>66768</t>
         </is>
@@ -3830,7 +3860,7 @@
           <t>TUCHSCHERER Lennard</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>60090</t>
         </is>
@@ -3888,7 +3918,7 @@
           <t>AMANBAYEV Adil</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>68999</t>
         </is>
@@ -3946,7 +3976,7 @@
           <t>DIACHUK Oleksii</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>39887</t>
         </is>
@@ -4004,7 +4034,7 @@
           <t>LAVIOLETTE Yannick</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>43343</t>
         </is>
@@ -4062,7 +4092,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -4120,7 +4150,7 @@
           <t>NOWAK Przemyslaw</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>43974</t>
         </is>
@@ -4178,7 +4208,7 @@
           <t>SMEDLEY Liam</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>36517</t>
         </is>
@@ -4236,7 +4266,7 @@
           <t>HENDRICK Robert</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
@@ -4294,7 +4324,7 @@
           <t>KULIKOV Alexandr</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>39679</t>
         </is>
@@ -4352,7 +4382,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -4410,7 +4440,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -4468,7 +4498,7 @@
           <t>MARZO Daniel</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
@@ -4526,7 +4556,7 @@
           <t>POMEROY Spencer</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>57783</t>
         </is>
@@ -4584,7 +4614,7 @@
           <t>FERNANDEZ Luis</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -4642,7 +4672,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -4700,7 +4730,7 @@
           <t>CRAWFORD Brodie</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>38436</t>
         </is>
@@ -4758,7 +4788,7 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -4816,7 +4846,7 @@
           <t>SHU Jianming</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>47327</t>
         </is>
@@ -4874,7 +4904,7 @@
           <t>CECCON Paolo</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>39903</t>
         </is>
@@ -4932,7 +4962,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -4990,7 +5020,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -5048,7 +5078,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -5106,7 +5136,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -5164,7 +5194,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -5222,7 +5252,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -5280,7 +5310,7 @@
           <t>JOLY Cedric</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>35681</t>
         </is>
@@ -5338,7 +5368,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -5396,7 +5426,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -5454,7 +5484,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -5512,7 +5542,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -5570,7 +5600,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -5628,7 +5658,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -5686,7 +5716,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -5744,7 +5774,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -5802,7 +5832,7 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -5860,7 +5890,7 @@
           <t>MIRGORODSKY Marko</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>42019</t>
         </is>
@@ -5918,7 +5948,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -5976,7 +6006,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -6034,7 +6064,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -6092,7 +6122,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -6150,7 +6180,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -6208,7 +6238,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -6266,7 +6296,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -6324,7 +6354,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -6382,7 +6412,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -6440,7 +6470,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -6498,7 +6528,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -6556,7 +6586,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -6614,7 +6644,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -6672,7 +6702,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -6730,7 +6760,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -6788,7 +6818,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -6846,7 +6876,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -6904,7 +6934,7 @@
           <t>ZHANG Yinuo</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
+      <c r="X110" t="inlineStr">
         <is>
           <t>43550</t>
         </is>
@@ -6962,7 +6992,7 @@
           <t>SALIKHOVA Karina</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>76711</t>
         </is>
@@ -7020,7 +7050,7 @@
           <t>SEPRENYI Sara Timea</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>52211</t>
         </is>
@@ -7078,7 +7108,7 @@
           <t>RAZEGHIAN Roxana</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>63124</t>
         </is>
@@ -7136,7 +7166,7 @@
           <t>CONLAN Aisling</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>35814</t>
         </is>
@@ -7194,7 +7224,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -7252,7 +7282,7 @@
           <t>OKAZAKI Haruka</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>42265</t>
         </is>
@@ -7310,7 +7340,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -7368,7 +7398,7 @@
           <t>OTTEN Maartje</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>35337</t>
         </is>
@@ -7426,7 +7456,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -7484,7 +7514,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -7542,7 +7572,7 @@
           <t>SRIBAR Ria</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>75645</t>
         </is>
@@ -7600,7 +7630,7 @@
           <t>WILLIAMS Courtney</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>68771</t>
         </is>
@@ -7658,7 +7688,7 @@
           <t>HAMER-EVANS Megan</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="X123" t="inlineStr">
         <is>
           <t>55138</t>
         </is>
@@ -7716,7 +7746,7 @@
           <t>DONNELLY Sage</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>60119</t>
         </is>
@@ -7774,7 +7804,7 @@
           <t>MITASIKOVA Monika</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>75445</t>
         </is>
@@ -7832,7 +7862,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="X126" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -7890,7 +7920,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="X127" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -7948,7 +7978,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -8006,7 +8036,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -8064,7 +8094,7 @@
           <t>OSCHMAUTZ Antonia</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>68839</t>
         </is>
@@ -8122,7 +8152,7 @@
           <t>GALUSKOVA Antonie</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>68754</t>
         </is>
@@ -8180,7 +8210,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -8238,7 +8268,7 @@
           <t>MINTALOVA Eliska</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>56169</t>
         </is>
@@ -8296,7 +8326,7 @@
           <t>HASSOVA Michaela</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>41783</t>
         </is>
@@ -8354,7 +8384,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -8412,7 +8442,7 @@
           <t>REN Ye</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>68810</t>
         </is>
@@ -8470,7 +8500,7 @@
           <t>LI Tong</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
@@ -8528,7 +8558,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -8586,7 +8616,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -8644,7 +8674,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -8702,7 +8732,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -8760,7 +8790,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -8818,7 +8848,7 @@
           <t>VALIKOVA Barbora</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>37267</t>
         </is>
@@ -8876,7 +8906,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -8934,7 +8964,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -8992,7 +9022,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -9050,7 +9080,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -9108,7 +9138,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -9166,7 +9196,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -9224,7 +9254,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -9282,7 +9312,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -9340,7 +9370,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -9398,7 +9428,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -9456,7 +9486,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -9514,7 +9544,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -9572,7 +9602,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -9630,7 +9660,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -9688,7 +9718,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -9746,7 +9776,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -9804,7 +9834,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -9862,7 +9892,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -9920,7 +9950,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -9978,7 +10008,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
+      <c r="X163" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -10036,7 +10066,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -10094,7 +10124,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -10152,7 +10182,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -10210,7 +10240,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -10268,7 +10298,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -10326,7 +10356,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -10384,7 +10414,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -10442,7 +10472,7 @@
           <t>TENG Zhiqiang</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>37089</t>
         </is>
@@ -10500,7 +10530,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -10558,7 +10588,7 @@
           <t>SHKLIARUK Nikolai</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>44025</t>
         </is>
@@ -10616,7 +10646,7 @@
           <t>DA SILVA Kaua</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>60500</t>
         </is>
@@ -10674,7 +10704,7 @@
           <t>ZHANG Genyuan</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>51818</t>
         </is>
@@ -10732,7 +10762,7 @@
           <t>SELBACH JUNIOR Gustavo</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>60496</t>
         </is>
@@ -10790,7 +10820,7 @@
           <t>KHRAMTSOV Dmitrii</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>66768</t>
         </is>
@@ -10848,7 +10878,7 @@
           <t>TUCHSCHERER Lennard</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>60090</t>
         </is>
@@ -10906,7 +10936,7 @@
           <t>AMANBAYEV Adil</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>68999</t>
         </is>
@@ -10964,7 +10994,7 @@
           <t>DIACHUK Oleksii</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>39887</t>
         </is>
@@ -11022,7 +11052,7 @@
           <t>LAVIOLETTE Yannick</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>43343</t>
         </is>
@@ -11080,7 +11110,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -11138,7 +11168,7 @@
           <t>NOWAK Przemyslaw</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>43974</t>
         </is>
@@ -11196,7 +11226,7 @@
           <t>SMEDLEY Liam</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>36517</t>
         </is>
@@ -11254,7 +11284,7 @@
           <t>HENDRICK Robert</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
@@ -11312,7 +11342,7 @@
           <t>KULIKOV Alexandr</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>39679</t>
         </is>
@@ -11370,7 +11400,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -11428,7 +11458,7 @@
           <t>MARZO Daniel</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
@@ -11486,7 +11516,7 @@
           <t>POMEROY Spencer</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>57783</t>
         </is>
@@ -11544,7 +11574,7 @@
           <t>FERNANDEZ Luis</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -11602,7 +11632,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -11660,7 +11690,7 @@
           <t>CRAWFORD Brodie</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>38436</t>
         </is>
@@ -11718,7 +11748,7 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -11776,7 +11806,7 @@
           <t>SHU Jianming</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>47327</t>
         </is>
@@ -11834,7 +11864,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -11892,7 +11922,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -11950,7 +11980,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -12008,7 +12038,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -12066,7 +12096,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -12124,7 +12154,7 @@
           <t>JOLY Cedric</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t>35681</t>
         </is>
@@ -12182,7 +12212,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
+      <c r="X201" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -12240,7 +12270,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -12298,7 +12328,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -12356,7 +12386,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -12414,7 +12444,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
+      <c r="X205" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -12472,7 +12502,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
+      <c r="X206" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -12530,7 +12560,7 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -12588,7 +12618,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
+      <c r="X208" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -12646,7 +12676,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -12704,7 +12734,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -12762,7 +12792,7 @@
           <t>ZHANG Yinuo</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>43550</t>
         </is>
@@ -12820,7 +12850,7 @@
           <t>SALIKHOVA Karina</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>76711</t>
         </is>
@@ -12878,7 +12908,7 @@
           <t>SEPRENYI Sara Timea</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>52211</t>
         </is>
@@ -12936,7 +12966,7 @@
           <t>RAZEGHIAN Roxana</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>63124</t>
         </is>
@@ -12994,7 +13024,7 @@
           <t>CONLAN Aisling</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>35814</t>
         </is>
@@ -13052,7 +13082,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
+      <c r="X216" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -13110,7 +13140,7 @@
           <t>OKAZAKI Haruka</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>42265</t>
         </is>
@@ -13168,7 +13198,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -13226,7 +13256,7 @@
           <t>OTTEN Maartje</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>35337</t>
         </is>
@@ -13284,7 +13314,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="X220" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -13342,7 +13372,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -13400,7 +13430,7 @@
           <t>SRIBAR Ria</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>75645</t>
         </is>
@@ -13458,7 +13488,7 @@
           <t>WILLIAMS Courtney</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>68771</t>
         </is>
@@ -13516,7 +13546,7 @@
           <t>HAMER-EVANS Megan</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>55138</t>
         </is>
@@ -13574,7 +13604,7 @@
           <t>DONNELLY Sage</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>60119</t>
         </is>
@@ -13632,7 +13662,7 @@
           <t>MITASIKOVA Monika</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>75445</t>
         </is>
@@ -13690,7 +13720,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -13748,7 +13778,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -13806,7 +13836,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -13864,7 +13894,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -13922,7 +13952,7 @@
           <t>OSCHMAUTZ Antonia</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>68839</t>
         </is>
@@ -13980,7 +14010,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
+      <c r="X232" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -14038,7 +14068,7 @@
           <t>MINTALOVA Eliska</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>56169</t>
         </is>
@@ -14096,7 +14126,7 @@
           <t>HASSOVA Michaela</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>41783</t>
         </is>
@@ -14154,7 +14184,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -14212,7 +14242,7 @@
           <t>REN Ye</t>
         </is>
       </c>
-      <c r="U236" t="inlineStr">
+      <c r="X236" t="inlineStr">
         <is>
           <t>68810</t>
         </is>
@@ -14270,7 +14300,7 @@
           <t>LI Tong</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr">
+      <c r="X237" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
@@ -14328,7 +14358,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
+      <c r="X238" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -14386,7 +14416,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -14444,7 +14474,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -14502,7 +14532,7 @@
           <t>VALIKOVA Barbora</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>37267</t>
         </is>
@@ -14560,7 +14590,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -14618,7 +14648,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -14676,7 +14706,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -14734,7 +14764,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -14792,7 +14822,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -14850,7 +14880,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -14908,7 +14938,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
+      <c r="X248" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -14966,7 +14996,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -15024,7 +15054,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -15082,7 +15112,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -15352,7 +15382,7 @@
           <t>MISHIMA Ren</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
+      <c r="X256" t="inlineStr">
         <is>
           <t>37757</t>
         </is>
@@ -15410,7 +15440,7 @@
           <t>ROLLINS Harriet</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>64680</t>
         </is>
@@ -15468,7 +15498,7 @@
           <t>CHEN Shiyu</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>84913</t>
         </is>
@@ -15526,7 +15556,7 @@
           <t>YANG Jie</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>43548</t>
         </is>
@@ -15584,7 +15614,7 @@
           <t>OGILVIE Sophie</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>53134</t>
         </is>
@@ -15642,7 +15672,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -15700,7 +15730,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -15758,7 +15788,7 @@
           <t>TRETIAKOVA Svetlana</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>68775</t>
         </is>
@@ -15816,7 +15846,7 @@
           <t>HAVLICKOVA Katerina</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>35048</t>
         </is>
@@ -15874,7 +15904,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -15932,7 +15962,7 @@
           <t>O'FERRALL Caoimhe</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
+      <c r="X266" t="inlineStr">
         <is>
           <t>61007</t>
         </is>
@@ -15990,7 +16020,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -16048,7 +16078,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -16106,7 +16136,7 @@
           <t>FORROW Bethan</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>69065</t>
         </is>
@@ -16164,7 +16194,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
+      <c r="X270" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -16222,7 +16252,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -16280,7 +16310,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -16338,7 +16368,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -16396,7 +16426,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="X274" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -16454,7 +16484,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -16512,7 +16542,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -16570,7 +16600,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr">
+      <c r="X277" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -16628,7 +16658,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -16686,7 +16716,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -16744,7 +16774,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
+      <c r="X280" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -16802,7 +16832,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
+      <c r="X281" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -16860,7 +16890,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -16918,7 +16948,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -16976,7 +17006,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -17034,7 +17064,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -17092,7 +17122,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -17150,7 +17180,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -17208,7 +17238,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U288" t="inlineStr">
+      <c r="X288" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -17266,7 +17296,7 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
+      <c r="X289" t="inlineStr">
         <is>
           <t>42016</t>
         </is>
@@ -17324,7 +17354,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr">
+      <c r="X290" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -17382,7 +17412,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
+      <c r="X291" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -17440,7 +17470,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr">
+      <c r="X292" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -17498,7 +17528,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -17556,7 +17586,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -17614,7 +17644,7 @@
           <t>DONNELLY Sage</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>60119</t>
         </is>
@@ -17672,7 +17702,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -17730,7 +17760,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -17788,7 +17818,7 @@
           <t>MATULKOVA Jana</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>37274</t>
         </is>
@@ -17846,7 +17876,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -17904,7 +17934,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -17962,7 +17992,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -18020,7 +18050,7 @@
           <t>ATMANAVICIUS Mantas</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>35619</t>
         </is>
@@ -18078,7 +18108,7 @@
           <t>PLATUKIS Augustas</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
+      <c r="X303" t="inlineStr">
         <is>
           <t>66435</t>
         </is>
@@ -18136,7 +18166,7 @@
           <t>ZHU Haoran</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
+      <c r="X304" t="inlineStr">
         <is>
           <t>43553</t>
         </is>
@@ -18194,7 +18224,7 @@
           <t>RASIMAVICIUS Vilius</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="X305" t="inlineStr">
         <is>
           <t>36965</t>
         </is>
@@ -18252,7 +18282,7 @@
           <t>SHABANOV Maxim</t>
         </is>
       </c>
-      <c r="U306" t="inlineStr">
+      <c r="X306" t="inlineStr">
         <is>
           <t>40575</t>
         </is>
@@ -18310,7 +18340,7 @@
           <t>STANOVSKY Samuel</t>
         </is>
       </c>
-      <c r="U307" t="inlineStr">
+      <c r="X307" t="inlineStr">
         <is>
           <t>84121</t>
         </is>
@@ -18368,7 +18398,7 @@
           <t>MCCREERY Alistair</t>
         </is>
       </c>
-      <c r="U308" t="inlineStr">
+      <c r="X308" t="inlineStr">
         <is>
           <t>60125</t>
         </is>
@@ -18426,7 +18456,7 @@
           <t>QUEMENEUR Malo</t>
         </is>
       </c>
-      <c r="U309" t="inlineStr">
+      <c r="X309" t="inlineStr">
         <is>
           <t>60403</t>
         </is>
@@ -18484,7 +18514,7 @@
           <t>RODRIGUES Fabio</t>
         </is>
       </c>
-      <c r="U310" t="inlineStr">
+      <c r="X310" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
@@ -18542,7 +18572,7 @@
           <t>TESTEN Niko</t>
         </is>
       </c>
-      <c r="U311" t="inlineStr">
+      <c r="X311" t="inlineStr">
         <is>
           <t>39980</t>
         </is>
@@ -18600,7 +18630,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
+      <c r="X312" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -18658,7 +18688,7 @@
           <t>GUBENKO Nikita</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
+      <c r="X313" t="inlineStr">
         <is>
           <t>39130</t>
         </is>
@@ -18716,7 +18746,7 @@
           <t>SIMPSON Keenan</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr">
+      <c r="X314" t="inlineStr">
         <is>
           <t>71797</t>
         </is>
@@ -18774,7 +18804,7 @@
           <t>TEAGUE Eoin</t>
         </is>
       </c>
-      <c r="U315" t="inlineStr">
+      <c r="X315" t="inlineStr">
         <is>
           <t>37913</t>
         </is>
@@ -18832,7 +18862,7 @@
           <t>KORPES Ren</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
+      <c r="X316" t="inlineStr">
         <is>
           <t>39941</t>
         </is>
@@ -18890,7 +18920,7 @@
           <t>SMITH Tyler</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>51904</t>
         </is>
@@ -18948,7 +18978,7 @@
           <t>KARLSSON Max</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
+      <c r="X318" t="inlineStr">
         <is>
           <t>35111</t>
         </is>
@@ -19006,7 +19036,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -19064,7 +19094,7 @@
           <t>WESTFALL Tyler</t>
         </is>
       </c>
-      <c r="U320" t="inlineStr">
+      <c r="X320" t="inlineStr">
         <is>
           <t>51919</t>
         </is>
@@ -19122,7 +19152,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr">
+      <c r="X321" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -19180,7 +19210,7 @@
           <t>TAN Ya</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
+      <c r="X322" t="inlineStr">
         <is>
           <t>52024</t>
         </is>
@@ -19238,7 +19268,7 @@
           <t>DANGEN Jack</t>
         </is>
       </c>
-      <c r="U323" t="inlineStr">
+      <c r="X323" t="inlineStr">
         <is>
           <t>51865</t>
         </is>
@@ -19296,7 +19326,7 @@
           <t>MUNSCH Manuel</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>35631</t>
         </is>
@@ -19354,7 +19384,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -19412,7 +19442,7 @@
           <t>DE DIONIGI Christian</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>43188</t>
         </is>
@@ -19470,7 +19500,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U327" t="inlineStr">
+      <c r="X327" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -19528,7 +19558,7 @@
           <t>KUDER MARUSIC Vid</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>44342</t>
         </is>
@@ -19586,7 +19616,7 @@
           <t>YOSHIDA Taku</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>41611</t>
         </is>
@@ -19644,7 +19674,7 @@
           <t>MAPELLI Guilherme</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -19702,7 +19732,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U331" t="inlineStr">
+      <c r="X331" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -19760,7 +19790,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -19818,7 +19848,7 @@
           <t>STANOVSKY Jakub</t>
         </is>
       </c>
-      <c r="U333" t="inlineStr">
+      <c r="X333" t="inlineStr">
         <is>
           <t>41781</t>
         </is>
@@ -19876,7 +19906,7 @@
           <t>VIANELLO Marco</t>
         </is>
       </c>
-      <c r="U334" t="inlineStr">
+      <c r="X334" t="inlineStr">
         <is>
           <t>54910</t>
         </is>
@@ -19934,7 +19964,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -19992,7 +20022,7 @@
           <t>BURGI Quentin</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>41590</t>
         </is>
@@ -20050,7 +20080,7 @@
           <t>YAZAWA Kazuki</t>
         </is>
       </c>
-      <c r="U337" t="inlineStr">
+      <c r="X337" t="inlineStr">
         <is>
           <t>36482</t>
         </is>
@@ -20108,7 +20138,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U338" t="inlineStr">
+      <c r="X338" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -20166,7 +20196,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U339" t="inlineStr">
+      <c r="X339" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -20224,7 +20254,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -20282,7 +20312,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -20340,7 +20370,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -20398,7 +20428,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U343" t="inlineStr">
+      <c r="X343" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -20456,7 +20486,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
+      <c r="X344" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -20514,7 +20544,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -20572,7 +20602,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U346" t="inlineStr">
+      <c r="X346" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -20630,7 +20660,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
+      <c r="X347" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -20688,7 +20718,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr">
+      <c r="X348" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -20746,7 +20776,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -20804,7 +20834,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr">
+      <c r="X350" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -20862,7 +20892,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -20920,7 +20950,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
+      <c r="X352" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -20978,7 +21008,7 @@
           <t>MAXEINER Tim</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>35117</t>
         </is>
@@ -21036,7 +21066,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U354" t="inlineStr">
+      <c r="X354" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -21094,7 +21124,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -21152,7 +21182,7 @@
           <t>HILGERT Lubos</t>
         </is>
       </c>
-      <c r="U356" t="inlineStr">
+      <c r="X356" t="inlineStr">
         <is>
           <t>35032</t>
         </is>
@@ -21210,7 +21240,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U357" t="inlineStr">
+      <c r="X357" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -21268,7 +21298,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr">
+      <c r="X358" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -21326,7 +21356,7 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
+      <c r="X359" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -21384,7 +21414,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U360" t="inlineStr">
+      <c r="X360" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -21442,7 +21472,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
+      <c r="X361" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -21500,7 +21530,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U362" t="inlineStr">
+      <c r="X362" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -21558,7 +21588,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
+      <c r="X363" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -21616,7 +21646,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U364" t="inlineStr">
+      <c r="X364" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -21674,7 +21704,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr">
+      <c r="X365" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -21732,7 +21762,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U366" t="inlineStr">
+      <c r="X366" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -21790,7 +21820,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr">
+      <c r="X367" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -21848,7 +21878,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U368" t="inlineStr">
+      <c r="X368" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -21906,7 +21936,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U369" t="inlineStr">
+      <c r="X369" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -21964,7 +21994,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr">
+      <c r="X370" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -22022,7 +22052,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
+      <c r="X371" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -22080,7 +22110,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U372" t="inlineStr">
+      <c r="X372" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -22138,7 +22168,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U373" t="inlineStr">
+      <c r="X373" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -22196,7 +22226,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U374" t="inlineStr">
+      <c r="X374" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -22254,7 +22284,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U375" t="inlineStr">
+      <c r="X375" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -22312,7 +22342,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U376" t="inlineStr">
+      <c r="X376" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -22370,7 +22400,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U377" t="inlineStr">
+      <c r="X377" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -22428,7 +22458,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U378" t="inlineStr">
+      <c r="X378" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -22486,7 +22516,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U379" t="inlineStr">
+      <c r="X379" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -22544,7 +22574,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U380" t="inlineStr">
+      <c r="X380" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -22602,7 +22632,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U381" t="inlineStr">
+      <c r="X381" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -22660,7 +22690,7 @@
           <t>MISHIMA Ren</t>
         </is>
       </c>
-      <c r="U382" t="inlineStr">
+      <c r="X382" t="inlineStr">
         <is>
           <t>37757</t>
         </is>
@@ -22718,7 +22748,7 @@
           <t>ROLLINS Harriet</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
+      <c r="X383" t="inlineStr">
         <is>
           <t>64680</t>
         </is>
@@ -22776,7 +22806,7 @@
           <t>CHEN Shiyu</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
+      <c r="X384" t="inlineStr">
         <is>
           <t>84913</t>
         </is>
@@ -22834,7 +22864,7 @@
           <t>YANG Jie</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr">
+      <c r="X385" t="inlineStr">
         <is>
           <t>43548</t>
         </is>
@@ -22892,7 +22922,7 @@
           <t>OGILVIE Sophie</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr">
+      <c r="X386" t="inlineStr">
         <is>
           <t>53134</t>
         </is>
@@ -22950,7 +22980,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U387" t="inlineStr">
+      <c r="X387" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -23008,7 +23038,7 @@
           <t>TRETIAKOVA Svetlana</t>
         </is>
       </c>
-      <c r="U388" t="inlineStr">
+      <c r="X388" t="inlineStr">
         <is>
           <t>68775</t>
         </is>
@@ -23066,7 +23096,7 @@
           <t>HAVLICKOVA Katerina</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="X389" t="inlineStr">
         <is>
           <t>35048</t>
         </is>
@@ -23124,7 +23154,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U390" t="inlineStr">
+      <c r="X390" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -23182,7 +23212,7 @@
           <t>O'FERRALL Caoimhe</t>
         </is>
       </c>
-      <c r="U391" t="inlineStr">
+      <c r="X391" t="inlineStr">
         <is>
           <t>61007</t>
         </is>
@@ -23240,7 +23270,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U392" t="inlineStr">
+      <c r="X392" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -23298,7 +23328,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U393" t="inlineStr">
+      <c r="X393" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -23356,7 +23386,7 @@
           <t>FORROW Bethan</t>
         </is>
       </c>
-      <c r="U394" t="inlineStr">
+      <c r="X394" t="inlineStr">
         <is>
           <t>69065</t>
         </is>
@@ -23414,7 +23444,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U395" t="inlineStr">
+      <c r="X395" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -23472,7 +23502,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
+      <c r="X396" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -23530,7 +23560,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U397" t="inlineStr">
+      <c r="X397" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -23588,7 +23618,7 @@
           <t>STACH Aleksandra</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
+      <c r="X398" t="inlineStr">
         <is>
           <t>61261</t>
         </is>
@@ -23646,7 +23676,7 @@
           <t>DONNELLY Sage</t>
         </is>
       </c>
-      <c r="U399" t="inlineStr">
+      <c r="X399" t="inlineStr">
         <is>
           <t>60119</t>
         </is>
@@ -23704,7 +23734,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U400" t="inlineStr">
+      <c r="X400" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -23762,7 +23792,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U401" t="inlineStr">
+      <c r="X401" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -23820,7 +23850,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U402" t="inlineStr">
+      <c r="X402" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -23878,7 +23908,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U403" t="inlineStr">
+      <c r="X403" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -23936,7 +23966,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U404" t="inlineStr">
+      <c r="X404" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -23994,7 +24024,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U405" t="inlineStr">
+      <c r="X405" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -24052,7 +24082,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U406" t="inlineStr">
+      <c r="X406" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -24110,7 +24140,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U407" t="inlineStr">
+      <c r="X407" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -24168,7 +24198,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U408" t="inlineStr">
+      <c r="X408" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -24226,7 +24256,7 @@
           <t>ATMANAVICIUS Mantas</t>
         </is>
       </c>
-      <c r="U409" t="inlineStr">
+      <c r="X409" t="inlineStr">
         <is>
           <t>35619</t>
         </is>
@@ -24284,7 +24314,7 @@
           <t>PLATUKIS Augustas</t>
         </is>
       </c>
-      <c r="U410" t="inlineStr">
+      <c r="X410" t="inlineStr">
         <is>
           <t>66435</t>
         </is>
@@ -24342,7 +24372,7 @@
           <t>ZHU Haoran</t>
         </is>
       </c>
-      <c r="U411" t="inlineStr">
+      <c r="X411" t="inlineStr">
         <is>
           <t>43553</t>
         </is>
@@ -24400,7 +24430,7 @@
           <t>RASIMAVICIUS Vilius</t>
         </is>
       </c>
-      <c r="U412" t="inlineStr">
+      <c r="X412" t="inlineStr">
         <is>
           <t>36965</t>
         </is>
@@ -24458,7 +24488,7 @@
           <t>SHABANOV Maxim</t>
         </is>
       </c>
-      <c r="U413" t="inlineStr">
+      <c r="X413" t="inlineStr">
         <is>
           <t>40575</t>
         </is>
@@ -24516,7 +24546,7 @@
           <t>MCCREERY Alistair</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
+      <c r="X414" t="inlineStr">
         <is>
           <t>60125</t>
         </is>
@@ -24574,7 +24604,7 @@
           <t>RODRIGUES Fabio</t>
         </is>
       </c>
-      <c r="U415" t="inlineStr">
+      <c r="X415" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
@@ -24632,7 +24662,7 @@
           <t>TESTEN Niko</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr">
+      <c r="X416" t="inlineStr">
         <is>
           <t>39980</t>
         </is>
@@ -24690,7 +24720,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U417" t="inlineStr">
+      <c r="X417" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -24748,7 +24778,7 @@
           <t>GUBENKO Nikita</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
+      <c r="X418" t="inlineStr">
         <is>
           <t>39130</t>
         </is>
@@ -24806,7 +24836,7 @@
           <t>SIMPSON Keenan</t>
         </is>
       </c>
-      <c r="U419" t="inlineStr">
+      <c r="X419" t="inlineStr">
         <is>
           <t>71797</t>
         </is>
@@ -24864,7 +24894,7 @@
           <t>TEAGUE Eoin</t>
         </is>
       </c>
-      <c r="U420" t="inlineStr">
+      <c r="X420" t="inlineStr">
         <is>
           <t>37913</t>
         </is>
@@ -24922,7 +24952,7 @@
           <t>KORPES Ren</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr">
+      <c r="X421" t="inlineStr">
         <is>
           <t>39941</t>
         </is>
@@ -24980,7 +25010,7 @@
           <t>SMITH Tyler</t>
         </is>
       </c>
-      <c r="U422" t="inlineStr">
+      <c r="X422" t="inlineStr">
         <is>
           <t>51904</t>
         </is>
@@ -25038,7 +25068,7 @@
           <t>KARLSSON Max</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr">
+      <c r="X423" t="inlineStr">
         <is>
           <t>35111</t>
         </is>
@@ -25096,7 +25126,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U424" t="inlineStr">
+      <c r="X424" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -25154,7 +25184,7 @@
           <t>WESTFALL Tyler</t>
         </is>
       </c>
-      <c r="U425" t="inlineStr">
+      <c r="X425" t="inlineStr">
         <is>
           <t>51919</t>
         </is>
@@ -25212,7 +25242,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U426" t="inlineStr">
+      <c r="X426" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -25270,7 +25300,7 @@
           <t>TAN Ya</t>
         </is>
       </c>
-      <c r="U427" t="inlineStr">
+      <c r="X427" t="inlineStr">
         <is>
           <t>52024</t>
         </is>
@@ -25328,7 +25358,7 @@
           <t>DANGEN Jack</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
+      <c r="X428" t="inlineStr">
         <is>
           <t>51865</t>
         </is>
@@ -25386,7 +25416,7 @@
           <t>MUNSCH Manuel</t>
         </is>
       </c>
-      <c r="U429" t="inlineStr">
+      <c r="X429" t="inlineStr">
         <is>
           <t>35631</t>
         </is>
@@ -25444,7 +25474,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U430" t="inlineStr">
+      <c r="X430" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -25502,7 +25532,7 @@
           <t>DE DIONIGI Christian</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
+      <c r="X431" t="inlineStr">
         <is>
           <t>43188</t>
         </is>
@@ -25560,7 +25590,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U432" t="inlineStr">
+      <c r="X432" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -25618,7 +25648,7 @@
           <t>KUDER MARUSIC Vid</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="X433" t="inlineStr">
         <is>
           <t>44342</t>
         </is>
@@ -25676,7 +25706,7 @@
           <t>YOSHIDA Taku</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr">
+      <c r="X434" t="inlineStr">
         <is>
           <t>41611</t>
         </is>
@@ -25734,7 +25764,7 @@
           <t>MAPELLI Guilherme</t>
         </is>
       </c>
-      <c r="U435" t="inlineStr">
+      <c r="X435" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -25792,7 +25822,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr">
+      <c r="X436" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -25850,7 +25880,7 @@
           <t>STANOVSKY Jakub</t>
         </is>
       </c>
-      <c r="U437" t="inlineStr">
+      <c r="X437" t="inlineStr">
         <is>
           <t>41781</t>
         </is>
@@ -25908,7 +25938,7 @@
           <t>VIANELLO Marco</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="X438" t="inlineStr">
         <is>
           <t>54910</t>
         </is>
@@ -25966,7 +25996,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr">
+      <c r="X439" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -26024,7 +26054,7 @@
           <t>YAZAWA Kazuki</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>36482</t>
         </is>
@@ -26082,7 +26112,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U441" t="inlineStr">
+      <c r="X441" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -26140,7 +26170,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr">
+      <c r="X442" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -26198,7 +26228,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="X443" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -26256,7 +26286,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="X444" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -26314,7 +26344,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U445" t="inlineStr">
+      <c r="X445" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -26372,7 +26402,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U446" t="inlineStr">
+      <c r="X446" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -26430,7 +26460,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U447" t="inlineStr">
+      <c r="X447" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -26488,7 +26518,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U448" t="inlineStr">
+      <c r="X448" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -26546,7 +26576,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U449" t="inlineStr">
+      <c r="X449" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -26604,7 +26634,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U450" t="inlineStr">
+      <c r="X450" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -26662,7 +26692,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U451" t="inlineStr">
+      <c r="X451" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -26720,7 +26750,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U452" t="inlineStr">
+      <c r="X452" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -26778,7 +26808,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="X453" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -26836,7 +26866,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="X454" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -26894,7 +26924,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U455" t="inlineStr">
+      <c r="X455" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -26952,7 +26982,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="X456" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -27010,7 +27040,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U457" t="inlineStr">
+      <c r="X457" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -27068,7 +27098,7 @@
           <t>STANOVSKY Samuel</t>
         </is>
       </c>
-      <c r="U458" t="inlineStr">
+      <c r="X458" t="inlineStr">
         <is>
           <t>84121</t>
         </is>
@@ -27338,7 +27368,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U463" t="inlineStr">
+      <c r="X463" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -27396,7 +27426,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U464" t="inlineStr">
+      <c r="X464" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -27454,7 +27484,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U465" t="inlineStr">
+      <c r="X465" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -27512,7 +27542,7 @@
           <t>TENG Zhiqiang</t>
         </is>
       </c>
-      <c r="U466" t="inlineStr">
+      <c r="X466" t="inlineStr">
         <is>
           <t>37089</t>
         </is>
@@ -27570,7 +27600,7 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U467" t="inlineStr">
+      <c r="X467" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -27628,7 +27658,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr">
+      <c r="X468" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -27686,7 +27716,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U469" t="inlineStr">
+      <c r="X469" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -27744,7 +27774,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="X470" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -27802,7 +27832,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U471" t="inlineStr">
+      <c r="X471" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -27860,7 +27890,7 @@
           <t>JOLY Cedric</t>
         </is>
       </c>
-      <c r="U472" t="inlineStr">
+      <c r="X472" t="inlineStr">
         <is>
           <t>35681</t>
         </is>
@@ -27918,7 +27948,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U473" t="inlineStr">
+      <c r="X473" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -27976,7 +28006,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U474" t="inlineStr">
+      <c r="X474" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -28034,7 +28064,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U475" t="inlineStr">
+      <c r="X475" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -28092,7 +28122,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U476" t="inlineStr">
+      <c r="X476" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -28150,7 +28180,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U477" t="inlineStr">
+      <c r="X477" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -28208,7 +28238,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U478" t="inlineStr">
+      <c r="X478" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -28266,7 +28296,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U479" t="inlineStr">
+      <c r="X479" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -28324,7 +28354,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U480" t="inlineStr">
+      <c r="X480" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -28382,7 +28412,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U481" t="inlineStr">
+      <c r="X481" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -28440,7 +28470,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U482" t="inlineStr">
+      <c r="X482" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -28498,7 +28528,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U483" t="inlineStr">
+      <c r="X483" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -28556,7 +28586,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U484" t="inlineStr">
+      <c r="X484" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -28614,7 +28644,7 @@
           <t>CECCON Paolo</t>
         </is>
       </c>
-      <c r="U485" t="inlineStr">
+      <c r="X485" t="inlineStr">
         <is>
           <t>39903</t>
         </is>
@@ -28672,7 +28702,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U486" t="inlineStr">
+      <c r="X486" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -28730,7 +28760,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U487" t="inlineStr">
+      <c r="X487" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -28788,7 +28818,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U488" t="inlineStr">
+      <c r="X488" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -28846,7 +28876,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U489" t="inlineStr">
+      <c r="X489" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -28904,7 +28934,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U490" t="inlineStr">
+      <c r="X490" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -28962,7 +28992,7 @@
           <t>MIRGORODSKY Marko</t>
         </is>
       </c>
-      <c r="U491" t="inlineStr">
+      <c r="X491" t="inlineStr">
         <is>
           <t>42019</t>
         </is>
@@ -29020,7 +29050,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U492" t="inlineStr">
+      <c r="X492" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -29078,7 +29108,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U493" t="inlineStr">
+      <c r="X493" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -29136,7 +29166,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U494" t="inlineStr">
+      <c r="X494" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -29194,7 +29224,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U495" t="inlineStr">
+      <c r="X495" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -29252,7 +29282,7 @@
           <t>VALIKOVA Barbora</t>
         </is>
       </c>
-      <c r="U496" t="inlineStr">
+      <c r="X496" t="inlineStr">
         <is>
           <t>37267</t>
         </is>
@@ -29310,7 +29340,7 @@
           <t>HASSOVA Michaela</t>
         </is>
       </c>
-      <c r="U497" t="inlineStr">
+      <c r="X497" t="inlineStr">
         <is>
           <t>41783</t>
         </is>
@@ -29368,7 +29398,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U498" t="inlineStr">
+      <c r="X498" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -29426,7 +29456,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U499" t="inlineStr">
+      <c r="X499" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -29484,7 +29514,7 @@
           <t>MINTALOVA Eliska</t>
         </is>
       </c>
-      <c r="U500" t="inlineStr">
+      <c r="X500" t="inlineStr">
         <is>
           <t>56169</t>
         </is>
@@ -29542,7 +29572,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
+      <c r="X501" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -29600,7 +29630,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U502" t="inlineStr">
+      <c r="X502" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -29658,7 +29688,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U503" t="inlineStr">
+      <c r="X503" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -29716,7 +29746,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U504" t="inlineStr">
+      <c r="X504" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -29774,7 +29804,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U505" t="inlineStr">
+      <c r="X505" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -29832,7 +29862,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U506" t="inlineStr">
+      <c r="X506" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -29890,7 +29920,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U507" t="inlineStr">
+      <c r="X507" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -29948,7 +29978,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="X508" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -30006,7 +30036,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U509" t="inlineStr">
+      <c r="X509" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -30064,7 +30094,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U510" t="inlineStr">
+      <c r="X510" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -30122,7 +30152,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U511" t="inlineStr">
+      <c r="X511" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -30180,7 +30210,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U512" t="inlineStr">
+      <c r="X512" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -30238,7 +30268,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U513" t="inlineStr">
+      <c r="X513" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -30296,7 +30326,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U514" t="inlineStr">
+      <c r="X514" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -30354,7 +30384,7 @@
           <t>GALUSKOVA Antonie</t>
         </is>
       </c>
-      <c r="U515" t="inlineStr">
+      <c r="X515" t="inlineStr">
         <is>
           <t>68754</t>
         </is>
@@ -30412,7 +30442,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U516" t="inlineStr">
+      <c r="X516" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -30470,7 +30500,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U517" t="inlineStr">
+      <c r="X517" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -30528,7 +30558,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U518" t="inlineStr">
+      <c r="X518" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -30586,7 +30616,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U519" t="inlineStr">
+      <c r="X519" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -30644,7 +30674,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U520" t="inlineStr">
+      <c r="X520" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -30702,7 +30732,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U521" t="inlineStr">
+      <c r="X521" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -30760,7 +30790,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U522" t="inlineStr">
+      <c r="X522" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -30828,7 +30858,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U523" t="inlineStr">
+      <c r="X523" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -30896,7 +30926,7 @@
           <t>JOLY Cedric</t>
         </is>
       </c>
-      <c r="U524" t="inlineStr">
+      <c r="X524" t="inlineStr">
         <is>
           <t>35681</t>
         </is>
@@ -30964,7 +30994,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U525" t="inlineStr">
+      <c r="X525" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -31032,7 +31062,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U526" t="inlineStr">
+      <c r="X526" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -31100,7 +31130,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U527" t="inlineStr">
+      <c r="X527" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -31168,7 +31198,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U528" t="inlineStr">
+      <c r="X528" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -31236,7 +31266,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U529" t="inlineStr">
+      <c r="X529" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -31304,7 +31334,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U530" t="inlineStr">
+      <c r="X530" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -31372,7 +31402,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U531" t="inlineStr">
+      <c r="X531" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -31440,7 +31470,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U532" t="inlineStr">
+      <c r="X532" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -31508,7 +31538,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U533" t="inlineStr">
+      <c r="X533" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -31576,7 +31606,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U534" t="inlineStr">
+      <c r="X534" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -31644,7 +31674,7 @@
           <t>MINTALOVA Eliska</t>
         </is>
       </c>
-      <c r="U535" t="inlineStr">
+      <c r="X535" t="inlineStr">
         <is>
           <t>56169</t>
         </is>
@@ -31712,7 +31742,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U536" t="inlineStr">
+      <c r="X536" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -31780,7 +31810,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U537" t="inlineStr">
+      <c r="X537" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -31848,7 +31878,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U538" t="inlineStr">
+      <c r="X538" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -31916,7 +31946,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U539" t="inlineStr">
+      <c r="X539" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -31984,7 +32014,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U540" t="inlineStr">
+      <c r="X540" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -32052,7 +32082,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U541" t="inlineStr">
+      <c r="X541" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -32120,7 +32150,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U542" t="inlineStr">
+      <c r="X542" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -32183,12 +32213,12 @@
           <t>POESCHEL Cindy</t>
         </is>
       </c>
-      <c r="U543" t="inlineStr">
+      <c r="X543" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V543" t="inlineStr">
+      <c r="Y543" t="inlineStr">
         <is>
           <t>36490</t>
         </is>
@@ -32251,12 +32281,12 @@
           <t>LAVIOLETTE Yannick</t>
         </is>
       </c>
-      <c r="U544" t="inlineStr">
+      <c r="X544" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
       </c>
-      <c r="V544" t="inlineStr">
+      <c r="Y544" t="inlineStr">
         <is>
           <t>43343</t>
         </is>
@@ -32319,12 +32349,12 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U545" t="inlineStr">
+      <c r="X545" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
       </c>
-      <c r="V545" t="inlineStr">
+      <c r="Y545" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -32387,12 +32417,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U546" t="inlineStr">
+      <c r="X546" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
       </c>
-      <c r="V546" t="inlineStr">
+      <c r="Y546" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -32455,12 +32485,12 @@
           <t>MRUZEK Vojtech</t>
         </is>
       </c>
-      <c r="U547" t="inlineStr">
+      <c r="X547" t="inlineStr">
         <is>
           <t>37274</t>
         </is>
       </c>
-      <c r="V547" t="inlineStr">
+      <c r="Y547" t="inlineStr">
         <is>
           <t>42012</t>
         </is>
@@ -32523,12 +32553,12 @@
           <t>XU Yongzhao</t>
         </is>
       </c>
-      <c r="U548" t="inlineStr">
+      <c r="X548" t="inlineStr">
         <is>
           <t>84750</t>
         </is>
       </c>
-      <c r="V548" t="inlineStr">
+      <c r="Y548" t="inlineStr">
         <is>
           <t>69446</t>
         </is>
@@ -32591,12 +32621,12 @@
           <t>XIE Yuancong</t>
         </is>
       </c>
-      <c r="U549" t="inlineStr">
+      <c r="X549" t="inlineStr">
         <is>
           <t>84749</t>
         </is>
       </c>
-      <c r="V549" t="inlineStr">
+      <c r="Y549" t="inlineStr">
         <is>
           <t>72214</t>
         </is>
@@ -32659,12 +32689,12 @@
           <t>ZHANG Genyuan</t>
         </is>
       </c>
-      <c r="U550" t="inlineStr">
+      <c r="X550" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
       </c>
-      <c r="V550" t="inlineStr">
+      <c r="Y550" t="inlineStr">
         <is>
           <t>51818</t>
         </is>
@@ -32727,7 +32757,7 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="V551" t="inlineStr">
+      <c r="Y551" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -32790,12 +32820,12 @@
           <t>HENRY Margaux</t>
         </is>
       </c>
-      <c r="U552" t="inlineStr">
+      <c r="X552" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
       </c>
-      <c r="V552" t="inlineStr">
+      <c r="Y552" t="inlineStr">
         <is>
           <t>51995</t>
         </is>
@@ -32858,12 +32888,12 @@
           <t>MASEK Jan</t>
         </is>
       </c>
-      <c r="U553" t="inlineStr">
+      <c r="X553" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
       </c>
-      <c r="V553" t="inlineStr">
+      <c r="Y553" t="inlineStr">
         <is>
           <t>36013</t>
         </is>
@@ -32926,7 +32956,7 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="V554" t="inlineStr">
+      <c r="Y554" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -32999,12 +33029,12 @@
           <t>ZHANG Genyuan</t>
         </is>
       </c>
-      <c r="U555" t="inlineStr">
+      <c r="X555" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
       </c>
-      <c r="V555" t="inlineStr">
+      <c r="Y555" t="inlineStr">
         <is>
           <t>51818</t>
         </is>
@@ -33077,12 +33107,12 @@
           <t>POESCHEL Cindy</t>
         </is>
       </c>
-      <c r="U556" t="inlineStr">
+      <c r="X556" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V556" t="inlineStr">
+      <c r="Y556" t="inlineStr">
         <is>
           <t>36490</t>
         </is>
@@ -33155,12 +33185,12 @@
           <t>XU Yongzhao</t>
         </is>
       </c>
-      <c r="U557" t="inlineStr">
+      <c r="X557" t="inlineStr">
         <is>
           <t>84750</t>
         </is>
       </c>
-      <c r="V557" t="inlineStr">
+      <c r="Y557" t="inlineStr">
         <is>
           <t>69446</t>
         </is>
@@ -33233,12 +33263,12 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U558" t="inlineStr">
+      <c r="X558" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
       </c>
-      <c r="V558" t="inlineStr">
+      <c r="Y558" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -33311,12 +33341,12 @@
           <t>MASEK Jan</t>
         </is>
       </c>
-      <c r="U559" t="inlineStr">
+      <c r="X559" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
       </c>
-      <c r="V559" t="inlineStr">
+      <c r="Y559" t="inlineStr">
         <is>
           <t>36013</t>
         </is>
@@ -33389,12 +33419,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U560" t="inlineStr">
+      <c r="X560" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
       </c>
-      <c r="V560" t="inlineStr">
+      <c r="Y560" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -33467,12 +33497,12 @@
           <t>MRUZEK Vojtech</t>
         </is>
       </c>
-      <c r="U561" t="inlineStr">
+      <c r="X561" t="inlineStr">
         <is>
           <t>37274</t>
         </is>
       </c>
-      <c r="V561" t="inlineStr">
+      <c r="Y561" t="inlineStr">
         <is>
           <t>42012</t>
         </is>
@@ -33545,12 +33575,12 @@
           <t>HENRY Margaux</t>
         </is>
       </c>
-      <c r="U562" t="inlineStr">
+      <c r="X562" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
       </c>
-      <c r="V562" t="inlineStr">
+      <c r="Y562" t="inlineStr">
         <is>
           <t>51995</t>
         </is>
@@ -33623,7 +33653,7 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="V563" t="inlineStr">
+      <c r="Y563" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -33696,7 +33726,7 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="V564" t="inlineStr">
+      <c r="Y564" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -33913,7 +33943,7 @@
           <t>STACH Aleksandra</t>
         </is>
       </c>
-      <c r="U568" t="inlineStr">
+      <c r="X568" t="inlineStr">
         <is>
           <t>61261</t>
         </is>
@@ -33971,7 +34001,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U569" t="inlineStr">
+      <c r="X569" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -34029,7 +34059,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U570" t="inlineStr">
+      <c r="X570" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -34087,7 +34117,7 @@
           <t>OGILVIE Sophie</t>
         </is>
       </c>
-      <c r="U571" t="inlineStr">
+      <c r="X571" t="inlineStr">
         <is>
           <t>53134</t>
         </is>
@@ -34145,7 +34175,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U572" t="inlineStr">
+      <c r="X572" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -34203,7 +34233,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U573" t="inlineStr">
+      <c r="X573" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -34261,7 +34291,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U574" t="inlineStr">
+      <c r="X574" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -34319,7 +34349,7 @@
           <t>HAVLICKOVA Katerina</t>
         </is>
       </c>
-      <c r="U575" t="inlineStr">
+      <c r="X575" t="inlineStr">
         <is>
           <t>35048</t>
         </is>
@@ -34377,7 +34407,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U576" t="inlineStr">
+      <c r="X576" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -34435,7 +34465,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U577" t="inlineStr">
+      <c r="X577" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -34493,7 +34523,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U578" t="inlineStr">
+      <c r="X578" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -34551,7 +34581,7 @@
           <t>MATULKOVA Jana</t>
         </is>
       </c>
-      <c r="U579" t="inlineStr">
+      <c r="X579" t="inlineStr">
         <is>
           <t>37274</t>
         </is>
@@ -34609,7 +34639,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U580" t="inlineStr">
+      <c r="X580" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -34667,7 +34697,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U581" t="inlineStr">
+      <c r="X581" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -34725,7 +34755,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U582" t="inlineStr">
+      <c r="X582" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -34783,7 +34813,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U583" t="inlineStr">
+      <c r="X583" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -34841,7 +34871,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U584" t="inlineStr">
+      <c r="X584" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -34899,7 +34929,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U585" t="inlineStr">
+      <c r="X585" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -34957,7 +34987,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U586" t="inlineStr">
+      <c r="X586" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -35015,7 +35045,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U587" t="inlineStr">
+      <c r="X587" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -35073,7 +35103,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U588" t="inlineStr">
+      <c r="X588" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -35131,7 +35161,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U589" t="inlineStr">
+      <c r="X589" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -35189,7 +35219,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U590" t="inlineStr">
+      <c r="X590" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -35247,7 +35277,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U591" t="inlineStr">
+      <c r="X591" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -35305,7 +35335,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U592" t="inlineStr">
+      <c r="X592" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -35363,7 +35393,7 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
-      <c r="U593" t="inlineStr">
+      <c r="X593" t="inlineStr">
         <is>
           <t>42016</t>
         </is>
@@ -35421,7 +35451,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U594" t="inlineStr">
+      <c r="X594" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -35479,7 +35509,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U595" t="inlineStr">
+      <c r="X595" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -35537,7 +35567,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U596" t="inlineStr">
+      <c r="X596" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -35595,7 +35625,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U597" t="inlineStr">
+      <c r="X597" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -35653,7 +35683,7 @@
           <t>KUDER MARUSIC Vid</t>
         </is>
       </c>
-      <c r="U598" t="inlineStr">
+      <c r="X598" t="inlineStr">
         <is>
           <t>44342</t>
         </is>
@@ -35711,7 +35741,7 @@
           <t>SHABANOV Maxim</t>
         </is>
       </c>
-      <c r="U599" t="inlineStr">
+      <c r="X599" t="inlineStr">
         <is>
           <t>40575</t>
         </is>
@@ -35769,7 +35799,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U600" t="inlineStr">
+      <c r="X600" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -35827,7 +35857,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U601" t="inlineStr">
+      <c r="X601" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -35885,7 +35915,7 @@
           <t>TESTEN Niko</t>
         </is>
       </c>
-      <c r="U602" t="inlineStr">
+      <c r="X602" t="inlineStr">
         <is>
           <t>39980</t>
         </is>
@@ -35943,7 +35973,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U603" t="inlineStr">
+      <c r="X603" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -36001,7 +36031,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U604" t="inlineStr">
+      <c r="X604" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -36059,7 +36089,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U605" t="inlineStr">
+      <c r="X605" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -36117,7 +36147,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U606" t="inlineStr">
+      <c r="X606" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -36175,7 +36205,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U607" t="inlineStr">
+      <c r="X607" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -36233,7 +36263,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U608" t="inlineStr">
+      <c r="X608" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -36291,7 +36321,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U609" t="inlineStr">
+      <c r="X609" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -36349,7 +36379,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U610" t="inlineStr">
+      <c r="X610" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -36407,7 +36437,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U611" t="inlineStr">
+      <c r="X611" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -36465,7 +36495,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U612" t="inlineStr">
+      <c r="X612" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -36523,7 +36553,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U613" t="inlineStr">
+      <c r="X613" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -36581,7 +36611,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U614" t="inlineStr">
+      <c r="X614" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -36639,7 +36669,7 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U615" t="inlineStr">
+      <c r="X615" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -36697,7 +36727,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U616" t="inlineStr">
+      <c r="X616" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -36755,7 +36785,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U617" t="inlineStr">
+      <c r="X617" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -36813,7 +36843,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U618" t="inlineStr">
+      <c r="X618" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -36871,7 +36901,7 @@
           <t>MAXEINER Tim</t>
         </is>
       </c>
-      <c r="U619" t="inlineStr">
+      <c r="X619" t="inlineStr">
         <is>
           <t>35117</t>
         </is>
@@ -36929,7 +36959,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U620" t="inlineStr">
+      <c r="X620" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -36987,7 +37017,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U621" t="inlineStr">
+      <c r="X621" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -37045,7 +37075,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U622" t="inlineStr">
+      <c r="X622" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -37103,7 +37133,7 @@
           <t>HILGERT Lubos</t>
         </is>
       </c>
-      <c r="U623" t="inlineStr">
+      <c r="X623" t="inlineStr">
         <is>
           <t>35032</t>
         </is>
@@ -37161,7 +37191,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U624" t="inlineStr">
+      <c r="X624" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -37219,7 +37249,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U625" t="inlineStr">
+      <c r="X625" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -37277,7 +37307,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U626" t="inlineStr">
+      <c r="X626" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -37335,7 +37365,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U627" t="inlineStr">
+      <c r="X627" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -37393,7 +37423,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U628" t="inlineStr">
+      <c r="X628" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -37451,7 +37481,7 @@
           <t>BURGI Quentin</t>
         </is>
       </c>
-      <c r="U629" t="inlineStr">
+      <c r="X629" t="inlineStr">
         <is>
           <t>41590</t>
         </is>
@@ -37509,7 +37539,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U630" t="inlineStr">
+      <c r="X630" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -37567,7 +37597,7 @@
           <t>QUEMENEUR Malo</t>
         </is>
       </c>
-      <c r="U631" t="inlineStr">
+      <c r="X631" t="inlineStr">
         <is>
           <t>60403</t>
         </is>
@@ -37625,7 +37655,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U632" t="inlineStr">
+      <c r="X632" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -37683,7 +37713,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U633" t="inlineStr">
+      <c r="X633" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -37741,7 +37771,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U634" t="inlineStr">
+      <c r="X634" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -37799,7 +37829,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U635" t="inlineStr">
+      <c r="X635" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -37857,7 +37887,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U636" t="inlineStr">
+      <c r="X636" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -37915,7 +37945,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U637" t="inlineStr">
+      <c r="X637" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -37983,7 +38013,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U638" t="inlineStr">
+      <c r="X638" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -38051,7 +38081,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U639" t="inlineStr">
+      <c r="X639" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -38119,7 +38149,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U640" t="inlineStr">
+      <c r="X640" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -38187,7 +38217,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U641" t="inlineStr">
+      <c r="X641" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -38255,7 +38285,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U642" t="inlineStr">
+      <c r="X642" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -38323,7 +38353,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U643" t="inlineStr">
+      <c r="X643" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -38391,7 +38421,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U644" t="inlineStr">
+      <c r="X644" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -38459,7 +38489,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U645" t="inlineStr">
+      <c r="X645" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -38527,7 +38557,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U646" t="inlineStr">
+      <c r="X646" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -38595,7 +38625,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U647" t="inlineStr">
+      <c r="X647" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -38663,7 +38693,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U648" t="inlineStr">
+      <c r="X648" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -38731,7 +38761,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U649" t="inlineStr">
+      <c r="X649" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -38799,7 +38829,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U650" t="inlineStr">
+      <c r="X650" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -38867,7 +38897,7 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U651" t="inlineStr">
+      <c r="X651" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -38935,7 +38965,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U652" t="inlineStr">
+      <c r="X652" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -39003,7 +39033,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U653" t="inlineStr">
+      <c r="X653" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -39071,7 +39101,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U654" t="inlineStr">
+      <c r="X654" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -39139,7 +39169,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U655" t="inlineStr">
+      <c r="X655" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -39207,7 +39237,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U656" t="inlineStr">
+      <c r="X656" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -39275,7 +39305,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U657" t="inlineStr">
+      <c r="X657" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -39338,7 +39368,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U658" t="inlineStr">
+      <c r="X658" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -39401,7 +39431,7 @@
           <t>DONNELLY Sage</t>
         </is>
       </c>
-      <c r="U659" t="inlineStr">
+      <c r="X659" t="inlineStr">
         <is>
           <t>60119</t>
         </is>
@@ -39464,7 +39494,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U660" t="inlineStr">
+      <c r="X660" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -39527,7 +39557,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U661" t="inlineStr">
+      <c r="X661" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -39590,7 +39620,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U662" t="inlineStr">
+      <c r="X662" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -39653,7 +39683,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U663" t="inlineStr">
+      <c r="X663" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -39716,7 +39746,7 @@
           <t>ROLLINS Harriet</t>
         </is>
       </c>
-      <c r="U664" t="inlineStr">
+      <c r="X664" t="inlineStr">
         <is>
           <t>64680</t>
         </is>
@@ -39779,7 +39809,7 @@
           <t>CHEN Shiyu</t>
         </is>
       </c>
-      <c r="U665" t="inlineStr">
+      <c r="X665" t="inlineStr">
         <is>
           <t>84913</t>
         </is>
@@ -39842,7 +39872,7 @@
           <t>HENRY Margaux</t>
         </is>
       </c>
-      <c r="U666" t="inlineStr">
+      <c r="X666" t="inlineStr">
         <is>
           <t>51995</t>
         </is>
@@ -39905,7 +39935,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U667" t="inlineStr">
+      <c r="X667" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -39968,7 +39998,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U668" t="inlineStr">
+      <c r="X668" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -40031,7 +40061,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U669" t="inlineStr">
+      <c r="X669" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -40094,7 +40124,7 @@
           <t>YANG Jie</t>
         </is>
       </c>
-      <c r="U670" t="inlineStr">
+      <c r="X670" t="inlineStr">
         <is>
           <t>43548</t>
         </is>
@@ -40157,7 +40187,7 @@
           <t>KARLSSON Max</t>
         </is>
       </c>
-      <c r="U671" t="inlineStr">
+      <c r="X671" t="inlineStr">
         <is>
           <t>35111</t>
         </is>
@@ -40220,7 +40250,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U672" t="inlineStr">
+      <c r="X672" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -40283,7 +40313,7 @@
           <t>QUEMENEUR Malo</t>
         </is>
       </c>
-      <c r="U673" t="inlineStr">
+      <c r="X673" t="inlineStr">
         <is>
           <t>60403</t>
         </is>
@@ -40346,7 +40376,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U674" t="inlineStr">
+      <c r="X674" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -40409,7 +40439,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U675" t="inlineStr">
+      <c r="X675" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -40472,7 +40502,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U676" t="inlineStr">
+      <c r="X676" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -40535,7 +40565,7 @@
           <t>STANOVSKY Jakub</t>
         </is>
       </c>
-      <c r="U677" t="inlineStr">
+      <c r="X677" t="inlineStr">
         <is>
           <t>41781</t>
         </is>
@@ -40656,7 +40686,7 @@
           <t>GUBENKO Nikita</t>
         </is>
       </c>
-      <c r="U679" t="inlineStr">
+      <c r="X679" t="inlineStr">
         <is>
           <t>39130</t>
         </is>
@@ -40719,7 +40749,7 @@
           <t>KORPES Ren</t>
         </is>
       </c>
-      <c r="U680" t="inlineStr">
+      <c r="X680" t="inlineStr">
         <is>
           <t>39941</t>
         </is>
@@ -40782,7 +40812,7 @@
           <t>RODRIGUES Fabio</t>
         </is>
       </c>
-      <c r="U681" t="inlineStr">
+      <c r="X681" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
@@ -40845,7 +40875,7 @@
           <t>WOS Michal</t>
         </is>
       </c>
-      <c r="U682" t="inlineStr">
+      <c r="X682" t="inlineStr">
         <is>
           <t>65063</t>
         </is>
@@ -40908,7 +40938,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U683" t="inlineStr">
+      <c r="X683" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -40971,7 +41001,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U684" t="inlineStr">
+      <c r="X684" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -41034,7 +41064,7 @@
           <t>STANOVSKY Samuel</t>
         </is>
       </c>
-      <c r="U685" t="inlineStr">
+      <c r="X685" t="inlineStr">
         <is>
           <t>84121</t>
         </is>
@@ -41097,7 +41127,7 @@
           <t>ZHU Haoran</t>
         </is>
       </c>
-      <c r="U686" t="inlineStr">
+      <c r="X686" t="inlineStr">
         <is>
           <t>43553</t>
         </is>
@@ -41160,7 +41190,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U687" t="inlineStr">
+      <c r="X687" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -41223,7 +41253,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U688" t="inlineStr">
+      <c r="X688" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -41286,7 +41316,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U689" t="inlineStr">
+      <c r="X689" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -41349,7 +41379,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U690" t="inlineStr">
+      <c r="X690" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -41412,7 +41442,7 @@
           <t>HENRY Margaux</t>
         </is>
       </c>
-      <c r="U691" t="inlineStr">
+      <c r="X691" t="inlineStr">
         <is>
           <t>51995</t>
         </is>
@@ -41475,7 +41505,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U692" t="inlineStr">
+      <c r="X692" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -41538,7 +41568,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U693" t="inlineStr">
+      <c r="X693" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -41601,7 +41631,7 @@
           <t>YANG Jie</t>
         </is>
       </c>
-      <c r="U694" t="inlineStr">
+      <c r="X694" t="inlineStr">
         <is>
           <t>43548</t>
         </is>
@@ -41664,7 +41694,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U695" t="inlineStr">
+      <c r="X695" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -41727,7 +41757,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U696" t="inlineStr">
+      <c r="X696" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -41790,7 +41820,7 @@
           <t>STANOVSKY Jakub</t>
         </is>
       </c>
-      <c r="U697" t="inlineStr">
+      <c r="X697" t="inlineStr">
         <is>
           <t>41781</t>
         </is>
@@ -41853,7 +41883,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U698" t="inlineStr">
+      <c r="X698" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -41916,7 +41946,7 @@
           <t>GUBENKO Nikita</t>
         </is>
       </c>
-      <c r="U699" t="inlineStr">
+      <c r="X699" t="inlineStr">
         <is>
           <t>39130</t>
         </is>
@@ -41979,7 +42009,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U700" t="inlineStr">
+      <c r="X700" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -42042,7 +42072,7 @@
           <t>WOS Michal</t>
         </is>
       </c>
-      <c r="U701" t="inlineStr">
+      <c r="X701" t="inlineStr">
         <is>
           <t>65063</t>
         </is>
@@ -42105,7 +42135,7 @@
           <t>ZHU Haoran</t>
         </is>
       </c>
-      <c r="U702" t="inlineStr">
+      <c r="X702" t="inlineStr">
         <is>
           <t>43553</t>
         </is>
@@ -42178,7 +42208,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U703" t="inlineStr">
+      <c r="X703" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -42241,7 +42271,7 @@
           <t>HENRY Margaux</t>
         </is>
       </c>
-      <c r="U704" t="inlineStr">
+      <c r="X704" t="inlineStr">
         <is>
           <t>51995</t>
         </is>
@@ -42314,7 +42344,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U705" t="inlineStr">
+      <c r="X705" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -42387,7 +42417,7 @@
           <t>YANG Jie</t>
         </is>
       </c>
-      <c r="U706" t="inlineStr">
+      <c r="X706" t="inlineStr">
         <is>
           <t>43548</t>
         </is>
@@ -42460,7 +42490,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U707" t="inlineStr">
+      <c r="X707" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -42533,7 +42563,7 @@
           <t>GUBENKO Nikita</t>
         </is>
       </c>
-      <c r="U708" t="inlineStr">
+      <c r="X708" t="inlineStr">
         <is>
           <t>39130</t>
         </is>
@@ -42606,7 +42636,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U709" t="inlineStr">
+      <c r="X709" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -42679,7 +42709,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U710" t="inlineStr">
+      <c r="X710" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -42746,7 +42776,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -42756,17 +42786,12 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="D712" t="inlineStr">
-        <is>
-          <t>Cross</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>Time Trials</t>
+          <t>Forerunner</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
@@ -42781,35 +42806,30 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>14:09:45</t>
+          <t>14:20:00</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="J712" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K712" t="n">
         <v>672</v>
       </c>
       <c r="R712" t="inlineStr">
         <is>
-          <t>SATILA Ana</t>
-        </is>
-      </c>
-      <c r="U712" t="inlineStr">
-        <is>
-          <t>35327</t>
+          <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -42819,12 +42839,12 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>Forerunner</t>
+          <t>Heats</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
@@ -42839,7 +42859,7 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>14:20:00</t>
+          <t>15:04:00</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -42848,138 +42868,17 @@
         </is>
       </c>
       <c r="J713" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K713" t="n">
         <v>673</v>
       </c>
       <c r="R713" t="inlineStr">
         <is>
-          <t>MAJERCZAK Grzegorz</t>
-        </is>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="B714" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C714" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E714" t="inlineStr">
-        <is>
-          <t>Semifinal</t>
-        </is>
-      </c>
-      <c r="F714" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G714" t="inlineStr">
-        <is>
-          <t>2018-07-03</t>
-        </is>
-      </c>
-      <c r="H714" t="inlineStr">
-        <is>
-          <t>14:40:00</t>
-        </is>
-      </c>
-      <c r="I714" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="J714" t="n">
-        <v>8</v>
-      </c>
-      <c r="K714" t="n">
-        <v>674</v>
-      </c>
-      <c r="R714" t="inlineStr">
-        <is>
-          <t>TILLARD Pierre-Antoine</t>
-        </is>
-      </c>
-      <c r="S714" t="inlineStr">
-        <is>
-          <t>PRIOUX Lucie</t>
-        </is>
-      </c>
-      <c r="U714" t="inlineStr">
-        <is>
-          <t>35413</t>
-        </is>
-      </c>
-      <c r="V714" t="inlineStr">
-        <is>
-          <t>42984</t>
-        </is>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="B715" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C715" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E715" t="inlineStr">
-        <is>
-          <t>Heats</t>
-        </is>
-      </c>
-      <c r="F715" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G715" t="inlineStr">
-        <is>
-          <t>2018-07-03</t>
-        </is>
-      </c>
-      <c r="H715" t="inlineStr">
-        <is>
-          <t>15:04:00</t>
-        </is>
-      </c>
-      <c r="I715" t="inlineStr">
-        <is>
-          <t>POL</t>
-        </is>
-      </c>
-      <c r="J715" t="n">
-        <v>30</v>
-      </c>
-      <c r="K715" t="n">
-        <v>675</v>
-      </c>
-      <c r="R715" t="inlineStr">
-        <is>
           <t>STACH Aleksandra</t>
         </is>
       </c>
-      <c r="U715" t="inlineStr">
+      <c r="X713" t="inlineStr">
         <is>
           <t>61261</t>
         </is>

--- a/events/Krakow_2018_WC/Krakow_2018_WC_start.xlsx
+++ b/events/Krakow_2018_WC/Krakow_2018_WC_start.xlsx
@@ -32757,6 +32757,11 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
+      <c r="X551" t="inlineStr">
+        <is>
+          <t>61261</t>
+        </is>
+      </c>
       <c r="Y551" t="inlineStr">
         <is>
           <t>35079</t>
@@ -32956,6 +32961,11 @@
           <t>JANE Jakub</t>
         </is>
       </c>
+      <c r="X554" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
       <c r="Y554" t="inlineStr">
         <is>
           <t>35061</t>
@@ -33653,6 +33663,11 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
+      <c r="X563" t="inlineStr">
+        <is>
+          <t>61261</t>
+        </is>
+      </c>
       <c r="Y563" t="inlineStr">
         <is>
           <t>35079</t>
@@ -33724,6 +33739,11 @@
       <c r="S564" t="inlineStr">
         <is>
           <t>JANE Jakub</t>
+        </is>
+      </c>
+      <c r="X564" t="inlineStr">
+        <is>
+          <t>42016</t>
         </is>
       </c>
       <c r="Y564" t="inlineStr">
